--- a/backend/data/Monthwise Report.xlsx
+++ b/backend/data/Monthwise Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Sep-24</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>Jul-26</t>
+  </si>
+  <si>
+    <t>Aug-26</t>
+  </si>
+  <si>
+    <t>Sep-26</t>
   </si>
   <si>
     <t>MONTH</t>
@@ -255,7 +261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8" customWidth="1"/>
@@ -285,73 +291,73 @@
   <sheetData>
     <row r="1" spans="1:23">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R1" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="T1" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:23">
@@ -430,13 +436,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>477000</v>
+        <v>476640</v>
       </c>
       <c r="C3" s="2">
         <v>55200</v>
       </c>
       <c r="D3" s="2">
-        <v>565080</v>
+        <v>565440</v>
       </c>
       <c r="E3" s="2">
         <v>21840</v>
@@ -445,10 +451,10 @@
         <v>1119120</v>
       </c>
       <c r="G3" s="2">
-        <v>103800</v>
+        <v>105240</v>
       </c>
       <c r="H3" s="2">
-        <v>16194</v>
+        <v>14754</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -475,22 +481,22 @@
         <v>58734</v>
       </c>
       <c r="Q3" s="3">
-        <v>36.753</v>
+        <v>36.725</v>
       </c>
       <c r="R3" s="3">
         <v>4.253</v>
       </c>
       <c r="S3" s="3">
-        <v>43.540</v>
+        <v>43.568</v>
       </c>
       <c r="T3" s="3">
         <v>1.683</v>
       </c>
       <c r="U3" s="3">
-        <v>7.998</v>
+        <v>8.109</v>
       </c>
       <c r="V3" s="3">
-        <v>1.248</v>
+        <v>1.137</v>
       </c>
       <c r="W3" s="3">
         <v>4.525</v>
@@ -501,13 +507,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>4937089</v>
+        <v>4938529</v>
       </c>
       <c r="C4" s="2">
         <v>186720</v>
       </c>
       <c r="D4" s="2">
-        <v>997910</v>
+        <v>996470</v>
       </c>
       <c r="E4" s="2">
         <v>67680</v>
@@ -546,13 +552,13 @@
         <v>105300</v>
       </c>
       <c r="Q4" s="3">
-        <v>77.864</v>
+        <v>77.887</v>
       </c>
       <c r="R4" s="3">
         <v>2.945</v>
       </c>
       <c r="S4" s="3">
-        <v>15.738</v>
+        <v>15.716</v>
       </c>
       <c r="T4" s="3">
         <v>1.067</v>
@@ -1921,70 +1927,212 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>16213850</v>
+        <v>21322730</v>
       </c>
       <c r="C24" s="2">
-        <v>105843</v>
+        <v>157783</v>
       </c>
       <c r="D24" s="2">
-        <v>1360397</v>
+        <v>1887177</v>
       </c>
       <c r="E24" s="2">
-        <v>89460</v>
+        <v>120120</v>
       </c>
       <c r="F24" s="2">
-        <v>17769550</v>
+        <v>23487810</v>
       </c>
       <c r="G24" s="2">
-        <v>69300</v>
+        <v>84980</v>
       </c>
       <c r="H24" s="2">
-        <v>85260</v>
+        <v>116620</v>
       </c>
       <c r="I24" s="2">
-        <v>35040</v>
+        <v>44840</v>
       </c>
       <c r="J24" s="2">
-        <v>189600</v>
+        <v>246440</v>
       </c>
       <c r="K24" s="2">
-        <v>64881</v>
+        <v>86338</v>
       </c>
       <c r="L24" s="2">
-        <v>74352</v>
+        <v>98119</v>
       </c>
       <c r="M24" s="2">
-        <v>7437</v>
+        <v>9609</v>
       </c>
       <c r="N24" s="2">
-        <v>16406</v>
+        <v>20933</v>
       </c>
       <c r="O24" s="2">
-        <v>51791</v>
+        <v>70693</v>
       </c>
       <c r="P24" s="2">
-        <v>214867</v>
+        <v>285692</v>
       </c>
       <c r="Q24" s="3">
-        <v>89.214</v>
+        <v>88.771</v>
       </c>
       <c r="R24" s="3">
-        <v>0.582</v>
+        <v>0.657</v>
       </c>
       <c r="S24" s="3">
-        <v>7.485</v>
+        <v>7.857</v>
       </c>
       <c r="T24" s="3">
-        <v>0.492</v>
+        <v>0.500</v>
       </c>
       <c r="U24" s="3">
-        <v>0.574</v>
+        <v>0.540</v>
       </c>
       <c r="V24" s="3">
-        <v>0.469</v>
+        <v>0.486</v>
       </c>
       <c r="W24" s="3">
-        <v>1.182</v>
+        <v>1.189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>19884300</v>
+      </c>
+      <c r="C25" s="2">
+        <v>141540</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2695120</v>
+      </c>
+      <c r="E25" s="2">
+        <v>188720</v>
+      </c>
+      <c r="F25" s="2">
+        <v>22909680</v>
+      </c>
+      <c r="G25" s="2">
+        <v>116760</v>
+      </c>
+      <c r="H25" s="2">
+        <v>58380</v>
+      </c>
+      <c r="I25" s="2">
+        <v>41160</v>
+      </c>
+      <c r="J25" s="2">
+        <v>216300</v>
+      </c>
+      <c r="K25" s="2">
+        <v>98594</v>
+      </c>
+      <c r="L25" s="2">
+        <v>113700</v>
+      </c>
+      <c r="M25" s="2">
+        <v>12120</v>
+      </c>
+      <c r="N25" s="2">
+        <v>21668</v>
+      </c>
+      <c r="O25" s="2">
+        <v>73960</v>
+      </c>
+      <c r="P25" s="2">
+        <v>320042</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>84.809</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0.604</v>
+      </c>
+      <c r="S25" s="3">
+        <v>11.495</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0.805</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0.674</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0.249</v>
+      </c>
+      <c r="W25" s="3">
+        <v>1.365</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>11844120</v>
+      </c>
+      <c r="C26" s="2">
+        <v>93660</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1040620</v>
+      </c>
+      <c r="E26" s="2">
+        <v>130760</v>
+      </c>
+      <c r="F26" s="2">
+        <v>13109160</v>
+      </c>
+      <c r="G26" s="2">
+        <v>84620</v>
+      </c>
+      <c r="H26" s="2">
+        <v>35980</v>
+      </c>
+      <c r="I26" s="2">
+        <v>33040</v>
+      </c>
+      <c r="J26" s="2">
+        <v>153640</v>
+      </c>
+      <c r="K26" s="2">
+        <v>60899</v>
+      </c>
+      <c r="L26" s="2">
+        <v>63547</v>
+      </c>
+      <c r="M26" s="2">
+        <v>7058</v>
+      </c>
+      <c r="N26" s="2">
+        <v>15568</v>
+      </c>
+      <c r="O26" s="2">
+        <v>43330</v>
+      </c>
+      <c r="P26" s="2">
+        <v>190402</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>88.039</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0.696</v>
+      </c>
+      <c r="S26" s="3">
+        <v>7.735</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0.972</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0.875</v>
+      </c>
+      <c r="V26" s="3">
+        <v>0.267</v>
+      </c>
+      <c r="W26" s="3">
+        <v>1.415</v>
       </c>
     </row>
   </sheetData>

--- a/backend/data/Monthwise Report.xlsx
+++ b/backend/data/Monthwise Report.xlsx
@@ -436,13 +436,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>476640</v>
+        <v>478320</v>
       </c>
       <c r="C3" s="2">
         <v>55200</v>
       </c>
       <c r="D3" s="2">
-        <v>565440</v>
+        <v>563760</v>
       </c>
       <c r="E3" s="2">
         <v>21840</v>
@@ -451,10 +451,10 @@
         <v>1119120</v>
       </c>
       <c r="G3" s="2">
-        <v>105240</v>
+        <v>103800</v>
       </c>
       <c r="H3" s="2">
-        <v>14754</v>
+        <v>16194</v>
       </c>
       <c r="I3" s="2">
         <v>0</v>
@@ -481,22 +481,22 @@
         <v>58734</v>
       </c>
       <c r="Q3" s="3">
-        <v>36.725</v>
+        <v>36.855</v>
       </c>
       <c r="R3" s="3">
         <v>4.253</v>
       </c>
       <c r="S3" s="3">
-        <v>43.568</v>
+        <v>43.438</v>
       </c>
       <c r="T3" s="3">
         <v>1.683</v>
       </c>
       <c r="U3" s="3">
-        <v>8.109</v>
+        <v>7.998</v>
       </c>
       <c r="V3" s="3">
-        <v>1.137</v>
+        <v>1.248</v>
       </c>
       <c r="W3" s="3">
         <v>4.525</v>
@@ -507,13 +507,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>4938529</v>
+        <v>4936849</v>
       </c>
       <c r="C4" s="2">
         <v>186720</v>
       </c>
       <c r="D4" s="2">
-        <v>996470</v>
+        <v>998150</v>
       </c>
       <c r="E4" s="2">
         <v>67680</v>
@@ -552,13 +552,13 @@
         <v>105300</v>
       </c>
       <c r="Q4" s="3">
-        <v>77.887</v>
+        <v>77.860</v>
       </c>
       <c r="R4" s="3">
         <v>2.945</v>
       </c>
       <c r="S4" s="3">
-        <v>15.716</v>
+        <v>15.742</v>
       </c>
       <c r="T4" s="3">
         <v>1.067</v>
@@ -2069,19 +2069,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>11844120</v>
+        <v>11868480</v>
       </c>
       <c r="C26" s="2">
         <v>93660</v>
       </c>
       <c r="D26" s="2">
-        <v>1040620</v>
+        <v>1048460</v>
       </c>
       <c r="E26" s="2">
         <v>130760</v>
       </c>
       <c r="F26" s="2">
-        <v>13109160</v>
+        <v>13141360</v>
       </c>
       <c r="G26" s="2">
         <v>84620</v>
@@ -2114,25 +2114,25 @@
         <v>190402</v>
       </c>
       <c r="Q26" s="3">
-        <v>88.039</v>
+        <v>88.010</v>
       </c>
       <c r="R26" s="3">
-        <v>0.696</v>
+        <v>0.695</v>
       </c>
       <c r="S26" s="3">
-        <v>7.735</v>
+        <v>7.775</v>
       </c>
       <c r="T26" s="3">
-        <v>0.972</v>
+        <v>0.970</v>
       </c>
       <c r="U26" s="3">
-        <v>0.875</v>
+        <v>0.872</v>
       </c>
       <c r="V26" s="3">
         <v>0.267</v>
       </c>
       <c r="W26" s="3">
-        <v>1.415</v>
+        <v>1.412</v>
       </c>
     </row>
   </sheetData>
